--- a/Excel_Solver.xlsx
+++ b/Excel_Solver.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bama365-my.sharepoint.com/personal/mewallace6_crimson_ua_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48806DB5-2116-4E81-9930-67348C6F8B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{5E9668C0-9C6B-4952-8AB2-1BE7AB382620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75DF5D3D-A42A-4FCD-84A3-489FEB0E34E7}"/>
   <bookViews>
-    <workbookView xWindow="6140" yWindow="1400" windowWidth="18740" windowHeight="14070" xr2:uid="{BD07B440-1C1C-4CFE-A59D-C9DB0080C75B}"/>
+    <workbookView xWindow="3730" yWindow="670" windowWidth="21150" windowHeight="14610" activeTab="1" xr2:uid="{BD07B440-1C1C-4CFE-A59D-C9DB0080C75B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Graphs" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$O$140:$O$151</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Data!$O$140:$O$151</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
@@ -30,7 +31,7 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$N$151</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Data!$N$151</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
@@ -446,6 +447,9701 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Methane:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Ideal Gas V vs T at 200bar</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.544180699436825E-2"/>
+                  <c:y val="-2.8985499895900718E-4"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Data!$F$11:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Data!$I$11:$I$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>0.12471</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1267885</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12886700000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13094550000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.133024</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13510250000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.13718100000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.13925950000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.14133800000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.1434165</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.14549500000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1475735</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.14965200000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.15173050000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.153809</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.15588750000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.15796600000000002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.16004450000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.16212300000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.1642015</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.16628000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.16835849999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.17043700000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.17251550000000002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.17459400000000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.17667250000000004</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.17875099999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.1808295</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.18290800000000002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.18498650000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.18706500000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.18914350000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.19122200000000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.19330049999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.195379</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.19745750000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.19953600000000002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.20161450000000003</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.20369300000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.2057715</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.20785000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.20992850000000002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.212007</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.21408550000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.21616400000000002</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.21824250000000003</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.22032099999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.2223995</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.22447800000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.22655650000000002</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.22863500000000003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.23071350000000002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.23279200000000003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.23487050000000001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.23694899999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.2390275</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.24110600000000001</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.24318450000000003</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.24526300000000004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.24734150000000002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.24942</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.25149850000000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.253577</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.25565550000000004</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.25773400000000002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.2598125</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.26189100000000004</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.26396950000000002</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.26604800000000001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.26812649999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.27020500000000003</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.27228350000000001</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.27436200000000005</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.27644050000000003</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.27851900000000002</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.2805975</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.28267600000000004</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.28475450000000002</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.286833</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.28891150000000004</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.29099000000000003</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.29306850000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.29514699999999999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.29722550000000003</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.29930400000000001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.30138250000000005</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.30346100000000004</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.30553950000000002</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.307618</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.30969650000000004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.31177500000000002</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.31385350000000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.31593200000000005</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.31801050000000003</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.32008900000000007</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.32216750000000005</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.32424600000000003</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.32632450000000007</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.328403</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.33048149999999998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.33256000000000002</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.33463850000000001</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.33671699999999999</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.33879550000000003</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.34087400000000001</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.34295250000000005</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.34503100000000003</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.34710950000000002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.34918800000000005</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.35126650000000004</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.35334500000000008</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.3554235</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.35750199999999999</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.35958050000000003</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.36165900000000001</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.36373749999999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.36581600000000003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.36789450000000001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.36997300000000005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.37205150000000003</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.37413000000000002</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.37620850000000006</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.37828700000000004</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.38036550000000008</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.38244400000000006</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.38452249999999999</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.38660099999999997</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.38867950000000001</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.39075799999999999</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.39283650000000003</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.39491500000000002</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.3969935</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.39907200000000004</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.40115050000000002</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.40322900000000006</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.40530750000000004</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.40738600000000003</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.40946450000000006</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.41154299999999999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.41362149999999998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.41570000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1B62-4789-8D9A-2E6AF65FEF65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1366728719"/>
+        <c:axId val="1366706159"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1366728719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000"/>
+          <c:min val="300"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperature (T)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366706159"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+        <c:minorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1366706159"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Molar Volume (L/mol)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1366728719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Methane:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> van der Waals V vs T at 200bar</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.7821411874707809E-2"/>
+                  <c:y val="-2.953875343895266E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Data!$F$11:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Data!$L$11:$L$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>0.10265886146971649</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10520107200062609</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10777981833502311</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11038934532285757</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.11302427775606927</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.11567957355509537</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.11835077264803417</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.12103379082102129</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.1237250426919433</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.12642140369914986</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.12912016897210485</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13181904679341472</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13451605952771059</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.13720958017251728</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.13989825102845657</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.14258094612783606</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.14525676906431201</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.14792496992096021</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.1505849932637551</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.15323639793052746</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.15587885634939086</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.1585121328887138</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.1611360707965695</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.16375058387170069</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.16635564285277973</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.16895124699787578</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.17153745587755923</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17411434746432067</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.17668202334772409</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.17924061601341654</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.18179024964293428</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.18433109155322033</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.18686330026747083</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.18938704233192649</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.1919024933631362</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.19440983042112309</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.19690923255817866</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.19940087879891547</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.20188494725314216</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.20436161957964979</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.20683106920209782</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.20929347028603307</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.21174899426985755</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.2141978090964162</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.2166400797354078</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.21907596756122319</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.22150563022062542</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.22392922166514567</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.22634689202978367</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.22875878573728411</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.23116504806148505</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.23356581645894975</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.23596122572700487</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.23835140299016033</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.2407364817658626</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.24311658314951085</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.24549182728319038</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.24786233083579468</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.2502282070857535</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.25258956600659782</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.25494651435439891</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.2572991544457281</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.25964758923769077</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.26199191625132462</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.26433222854441957</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.26666861889221022</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.2690011766031376</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.2713299883797029</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.27365513840107225</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.275976708403815</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.2782947767012468</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.28060942355724727</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.28292072066663143</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.28522873822394595</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.28753355376126782</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.28983523274458106</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.29213384514245999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.29442944590566539</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.29672210798727772</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.29901188938133821</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.30129885397561273</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.30358305138362579</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.30586454203898383</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.30814337590509827</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.31041961595628492</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.31269330942537621</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.31496451141425386</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.31723325743388875</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.31949960912861652</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.32176360855503783</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.32402530114715933</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.32628473116109041</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.32854194718892754</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.3307969748124589</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.33304987140266729</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.33530067703019223</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.3375494136717051</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.3397961361812406</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.34204088149159084</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.34428366891176737</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.34652455041219971</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.34876355470439496</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.35100072111423608</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.35323606487185377</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.35546964114014956</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.35770146360532284</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.35993156279778449</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.36215997988593007</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.3643867381088795</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.36661187117479588</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.36883539059775983</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.37105733956511427</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.37327773910732331</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.37549661503984016</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.37771399703732644</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.37992990063114579</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.38214435460998625</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.38435738255516599</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.38656900752796297</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.38877925208401271</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.39098813564960527</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.39319568545359623</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.39540191962903448</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.39760685961611292</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.39981052387306559</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.40201293318806403</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.40421410780481543</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.40641406748445541</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.40861282415898892</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.41081040405885988</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.41300682197398719</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.41520209424239929</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.41739623995406638</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.41958927498540538</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.42178121575043398</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.42397207833395995</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.42616187849990983</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.42835063169940479</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.43053835307859284</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.43272505748624512</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.43491076624417491</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8CC7-4C28-BD6A-E743B988D300}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="180129903"/>
+        <c:axId val="183852639"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="180129903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000"/>
+          <c:min val="300"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperature</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (T)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="183852639"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="183852639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Molar Volume (L/mol)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="180129903"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Methane:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Redlich Kwong V vs T at 200bar</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-4.9268204868571135E-2"/>
+                  <c:y val="-2.0485044391682264E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Data!$F$11:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Data!$O$11:$O$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>0.10523690081603879</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10826370679400109</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11127374634055386</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11426481716739476</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.11723531958945228</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.12018422574375533</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.12311090797408913</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.12601505673749455</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.12889664468323486</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13175579379934182</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13459282501778819</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13740814384256322</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.14020225605005407</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14297571120773386</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14572908453588754</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.14846299298518664</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.15117806319554389</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.15387492555664065</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.15655419235234833</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.1592164851989675</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.16186241021877604</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.16449255208035074</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.16710748298846573</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.16970775550592399</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.17229390493251109</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.17486644526414949</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.17742587222412498</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17997266223906189</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.18250727272660527</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.18503014129885575</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.18754168962549819</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.19004232038356936</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.19253241958311593</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.19501235695690303</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.19748248655883283</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.19994314631442728</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.20239466412781001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.20483734571963341</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.20727149318768989</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.20969739024925277</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.21211531320284452</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.21452551454820437</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.21692825822601286</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.21932377042822795</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.22171229711971568</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.22409404359651527</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.2264692343231601</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.22883806896006906</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.23120074309051999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.23355744453918797</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.23590835373629068</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.23825364431183607</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.24059348265826747</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.24292802859583912</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.24525744067625668</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.24758185614904157</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.2499014284222815</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.25221629967213638</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.25452658733041489</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.25683242555249763</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.25913393720134731</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.26143122461633522</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.26372443228439302</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.26601365616329303</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.26829900254408295</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.27058057401159513</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.27285847258815199</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.27513278495651639</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.27740361245771439</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.27967104137213455</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.28193515797628421</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.28419604568036277</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.2864537896323146</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.28870845439472992</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.29096013390011422</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.29320888700661418</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.2954547891761109</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.29769790319358164</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.29993830655756842</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.30217606423142102</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.30441121998859672</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.30664385268131961</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.30887401465753445</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.31110176265823336</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.31332715171822895</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.31555023522956255</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.31777106500212132</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.3199896991932385</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.32220616300497018</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.32442052745349276</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.32663283070354177</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.32884311747520123</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.33105143121883163</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.33325781415967515</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.33546230734059901</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.33766495997443208</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.339865782926419</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.34206484186555225</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.34426216418705835</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.34645778560390933</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.34865174086874778</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.35084406380585015</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.35303478734182403</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.35522394353509584</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.35741156360424614</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.35959767795524306</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.3617823162076238</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.36396550721967108</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.36614729023604331</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.36832765929400685</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.37050667447998825</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.37268435071702488</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.37486071340260879</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.37703579897725958</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.37920959658391951</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.38138217667779367</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.38355352693420497</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.38572368156491654</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.38789266246926568</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.39006047878407824</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.39222717577029326</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.39439276165212422</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.39655725632635874</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.39872067922519139</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.40088304932964169</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.40304438518251001</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.40520471769235261</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.40736402618825374</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.40952236634613076</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.41167974228538978</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.41383618359751756</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.41599166726330478</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.41814624826675345</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.42029992900122193</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.42245272458081734</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.42460464978924922</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.42675571908875576</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.42890594662874254</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.43105534625414421</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.43320393151352049</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.43535172927154947</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E7BC-4411-83F2-86C816ED0E55}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1622596047"/>
+        <c:axId val="181619359"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1622596047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000"/>
+          <c:min val="300"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperature (T)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="181619359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="181619359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Molar Volume (L/mol)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1622596047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Methane: SRK V vs T at 200bar</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.008450704225352E-2"/>
+                  <c:y val="-5.9374781542137741E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Data!$F$11:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Data!$R$11:$R$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>0.10800960061721698</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11119297926016077</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.11435420609792964</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11749124270884899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12060266367432737</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.12368767593556823</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.12674585719374051</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.12977713122503148</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.13278165190640218</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13575978698171656</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13871203403797672</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.14163897974016748</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.14454128557223245</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.14741965866884699</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.15027482230707151</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.15310752621709464</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.15591851604795431</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.15870853129205942</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.16147830196697968</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.16422853940337739</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.16695993796443312</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.1696731709138122</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.17236888938557646</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.17504771786253823</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.17771026456701358</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.18035710908502367</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.18298880933576367</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.18560590060005319</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.18820889609691832</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.19079828765410814</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.1933745464410962</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.19593812374030489</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.19848945173804092</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.20102894432095586</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.20355699786745288</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.20607399202613466</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.20858029047562404</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.21107624166165909</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.2135621795086754</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.21603842524992764</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.2185052858469963</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.22096305640964509</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.22341201790198917</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.22585244130700954</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.2282845867632956</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.23070870408255242</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.23312501974052585</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.23553378917866793</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.2379352227387419</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.24032953360623582</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.24271692685528706</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.24509759982562895</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.24747174247991655</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.24983953774237719</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.25220116181971325</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.25455678450534847</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.25690656946772483</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.25925067452376122</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.26158925189807775</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.26392244846885221</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.26625040600113947</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.26857326136818982</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.27089114676159975</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.27320418989080469</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.27551251417250522</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.27781623891079033</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.28011547946814175</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.28241034742807047</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.28470095074989199</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.28698739391576783</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.28926977807083126</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.29154820115644287</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.29382275803725427</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.29609354062200244</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.29836063797892387</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.3006241364456006</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.30288411973370755</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.30514066902908393</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.30739386308705402</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.30964377832356865</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.31189048890221016</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.31413406681723288</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.31637458197307144</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.31861210226015696</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.32084669362758989</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.3230784201526043</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.32530734410700085</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.32753352602077523</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.32975702474298613</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.33197789750023715</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.33419619995247452</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.33641198624662333</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.33862530906795274</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.34083621968939865</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.3430447680187596</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.34525100264412728</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.34745497087737592</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.34965671879606153</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.3518562912834835</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.35405373206733443</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.35624908375676256</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.35844238787804095</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.36063368490876291</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.36282301431093339</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.36501041456258454</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.36719592318830035</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.36937957678865768</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.37156141106851548</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.37374146086415838</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.37591976016964312</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.3780963421620262</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.38027123922579731</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.38244448297627731</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.38461609336169039</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.38678613328846584</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.3889545994352257</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.39112153148026013</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.39328695751764986</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.39545090499682761</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.39761340074093643</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.3997744709645043</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.4019341412905198</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.40409243676692819</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.40624938188252308</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.40840500058246515</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.41055931628307557</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.41271235188631589</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.41486412979367299</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.41701467191969294</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.41916399970499202</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.42131213412886687</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.42345909572156482</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.4256049045760823</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.42774958035965444</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.42989314232472597</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.432035609319951</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.43417699980029695</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.4363173318374432</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.43845662312931977</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.44059489100971017</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.44273215245741482</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4335-4B71-9EE3-A67263D21DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="189476207"/>
+        <c:axId val="189474767"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="189476207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000"/>
+          <c:min val="300"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperature (T)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="189474767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="189474767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Molar Volume (L/mol)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="189476207"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Methan</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>e: Peng Robinson V vs T at 200bar</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.0880149812734081E-2"/>
+                  <c:y val="-2.3915650249601152E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Data!$F$11:$F$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Data!$U$11:$U$151</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="141"/>
+                <c:pt idx="0">
+                  <c:v>0.10120812914997228</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10431529273601113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10740412615704448</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11047266583516135</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.11351956147454491</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.1165439424125405</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.11954534012578888</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.12252355961406924</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.12547864174479742</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.12841080019036286</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13132037798602528</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.13420782108429058</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.13707361707350446</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.13991833032915652</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14274254201929712</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.1455468640463862</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.14833189576352038</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.15109824939069619</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.15384653001818763</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.15657733333876978</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.1592912425272805</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.1619888260016196</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.16467063587275763</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.16733720693188178</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.16998905605407513</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.17262668192357977</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.17525056500549413</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17786116770439708</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.18045893466311019</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.18304429316458645</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.18561765360804944</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.18817941003630925</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.19072994069660276</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.19326960862103673</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.19579876221577663</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.19831773585093976</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.20082685044453275</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.20332641403611232</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.20581672234648557</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.2082980593209581</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.21077069765438178</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.21323489929704906</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.21569091594050885</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.21813898948346069</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.22057935247714097</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.22301222855107503</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.22543783281902402</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.2278563722661244</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.23026804611722759</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.23267304618785412</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.23507155721763368</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.23746375718765902</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.23984981762198559</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.24222990387414339</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.24460417539952314</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.24697278601410572</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.24933588414026536</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.25169361304046717</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.25404611103920782</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.2563935117340635</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.25873594419622875</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.26107353316115695</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.26340639920997233</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.2657346589418641</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.2680584251382187</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.27037780691866892</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.27269290988974698</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.27500383628639596</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.27731068510670742</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.27961355224026696</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.28191253059057447</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.28420771019159369</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.28649917831893923</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.28878701959601494</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.29107131609512776</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.29335214743417332</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.29562959086873364</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.29790372138027982</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.30017461176019833</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.30244233269027487</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.30470695281953747</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.30696853883775266</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.30922715554576125</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.31148286592274865</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.31373573119063547</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.31598581087574901</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.31823316286789721</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.32047784347691211</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.32271990748690044</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.32495940820820712</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.32719639752727026</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.32943092595444801</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.33166304266985752</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.33389279556744933</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.33612023129724383</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.33834539530593999</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.34056833187591695</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.34278908416269588</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.34500769423094724</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.34722420308911989</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.34943865072274566</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.35165107612643937</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.35386151733473586</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.35607001145175499</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.35827659467971329</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.3604813023464532</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.36268416893190603</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.36488522809359686</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.36708451269123044</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.36928205481038745</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.37147788578536289</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.37367203622118678</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.37586453601488595</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.37805541437596507</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.38024469984622272</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.38243242031878633</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.38461860305660067</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.38680327471020048</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.38898646133491244</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.39116818840745593</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.39334848084200347</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.39552736300568425</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.39770485873358097</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.39988099134323057</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.40205578364863848</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.40422925797384707</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.40640143616605506</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.40857233960831929</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.4107419892318232</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.41291040552779512</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.41507760855902426</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.41724361797099302</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.41940845300270463</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.4215721324971351</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.42373467491137723</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.42589609832646408</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.42805642045690151</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.43021565865990108</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.43237382994432844</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.43453095097938416</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.43668703203211101</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F13E-4FCC-8B61-7FA0F00ABF77}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="182751599"/>
+        <c:axId val="182752559"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="182751599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000"/>
+          <c:min val="300"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperature</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (T)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="182752559"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="182752559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Molar Volume (L/mol)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="182751599"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>257173</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>28573</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1448D40-52BD-485F-98C2-2456ED89FC6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>180974</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E8E42B-22FE-41BE-81F8-958B61091D04}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>266699</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A628562-B64A-4807-AF38-802C70E06A9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15C9A6AD-B728-4239-8C58-0CD0CE3D4D5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74D4DD9D-D8E8-4E14-B341-51D9708C1EEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -796,7 +10492,7 @@
     <col min="1" max="1" width="18.26953125" customWidth="1"/>
     <col min="3" max="3" width="8.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.08984375" customWidth="1"/>
     <col min="9" max="9" width="12.453125" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.26953125" bestFit="1" customWidth="1"/>
@@ -8703,27 +18399,20 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100081C3-AB8D-4E8D-AC70-EB6C7EDD4B25}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1ddcabea-40c9-47f6-bc94-41d8d375876f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B5FA33D4DE4894C85FE06DB2C306457" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623cefbe8a28ef174b8fa42e9c2fddda">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="1ddcabea-40c9-47f6-bc94-41d8d375876f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="96d16e63899c0d1759bb974bbb07beb8" ns3:_="">
-    <xsd:import namespace="1ddcabea-40c9-47f6-bc94-41d8d375876f"/>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009E69E45A62D5B7459DBFFA8232EBF894" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95b92b34a394c198fd7f8c00503417bf">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0c511fbd-96c6-4db7-861d-163d8dbbdfa9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="32cf1609781f1a9dd8b030cb397ff581" ns3:_="">
+    <xsd:import namespace="0c511fbd-96c6-4db7-861d-163d8dbbdfa9"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -8736,6 +18425,10 @@
                 <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -8743,7 +18436,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1ddcabea-40c9-47f6-bc94-41d8d375876f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0c511fbd-96c6-4db7-861d-163d8dbbdfa9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -8774,6 +18467,28 @@
     <xsd:element name="_activity" ma:index="13" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="14" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -8876,38 +18591,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F6AD431-5213-4F35-9C58-285077A995CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0c511fbd-96c6-4db7-861d-163d8dbbdfa9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D486AB69-1ED9-454B-9AC6-C6F8E65BE0E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="1ddcabea-40c9-47f6-bc94-41d8d375876f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{475A70D3-EDA1-4882-A35A-DA79FB035DB2}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB9E4D2E-8AF7-4C5A-99F7-C04754C33798}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1ddcabea-40c9-47f6-bc94-41d8d375876f"/>
+    <ds:schemaRef ds:uri="0c511fbd-96c6-4db7-861d-163d8dbbdfa9"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -8916,4 +18624,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D486AB69-1ED9-454B-9AC6-C6F8E65BE0E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="0c511fbd-96c6-4db7-861d-163d8dbbdfa9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F6AD431-5213-4F35-9C58-285077A995CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>